--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/GEORGIA_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/GEORGIA_2021.xlsx
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C132">
@@ -3199,7 +3199,7 @@
         <v>19</v>
       </c>
       <c r="D158">
-        <v>0.0009269649216958579</v>
+        <v>0.000926964921695858</v>
       </c>
     </row>
     <row r="159">
@@ -3433,7 +3433,7 @@
         <v>19</v>
       </c>
       <c r="D171">
-        <v>0.0009269649216958579</v>
+        <v>0.000926964921695858</v>
       </c>
     </row>
     <row r="172">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C178">
@@ -4045,7 +4045,7 @@
         <v>20</v>
       </c>
       <c r="D205">
-        <v>0.0009757525491535347</v>
+        <v>0.0009757525491535348</v>
       </c>
     </row>
     <row r="206">
@@ -4135,7 +4135,7 @@
         <v>19</v>
       </c>
       <c r="D210">
-        <v>0.0009269649216958579</v>
+        <v>0.000926964921695858</v>
       </c>
     </row>
     <row r="211">
@@ -4801,7 +4801,7 @@
         <v>19</v>
       </c>
       <c r="D247">
-        <v>0.0009269649216958579</v>
+        <v>0.000926964921695858</v>
       </c>
     </row>
     <row r="248">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C293">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C303">
@@ -5827,7 +5827,7 @@
         <v>19</v>
       </c>
       <c r="D304">
-        <v>0.0009269649216958579</v>
+        <v>0.000926964921695858</v>
       </c>
     </row>
     <row r="305">
@@ -6277,7 +6277,7 @@
         <v>19</v>
       </c>
       <c r="D329">
-        <v>0.0009269649216958579</v>
+        <v>0.000926964921695858</v>
       </c>
     </row>
     <row r="330">
@@ -7735,7 +7735,7 @@
         <v>20</v>
       </c>
       <c r="D410">
-        <v>0.0009757525491535347</v>
+        <v>0.0009757525491535348</v>
       </c>
     </row>
     <row r="411">
@@ -8869,7 +8869,7 @@
         <v>19</v>
       </c>
       <c r="D473">
-        <v>0.0009269649216958579</v>
+        <v>0.000926964921695858</v>
       </c>
     </row>
     <row r="474">
@@ -10759,7 +10759,7 @@
         <v>19</v>
       </c>
       <c r="D578">
-        <v>0.0009269649216958579</v>
+        <v>0.000926964921695858</v>
       </c>
     </row>
     <row r="579">
@@ -12343,7 +12343,7 @@
         <v>19</v>
       </c>
       <c r="D666">
-        <v>0.0009269649216958579</v>
+        <v>0.000926964921695858</v>
       </c>
     </row>
     <row r="667">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C720">
@@ -13657,7 +13657,7 @@
         <v>20</v>
       </c>
       <c r="D739">
-        <v>0.0009757525491535347</v>
+        <v>0.0009757525491535348</v>
       </c>
     </row>
     <row r="740">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C836">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C837">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C877">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C883">
@@ -19561,7 +19561,7 @@
         <v>19</v>
       </c>
       <c r="D1067">
-        <v>0.0009269649216958579</v>
+        <v>0.000926964921695858</v>
       </c>
     </row>
     <row r="1068">
@@ -20929,7 +20929,7 @@
         <v>20</v>
       </c>
       <c r="D1143">
-        <v>0.0009757525491535347</v>
+        <v>0.0009757525491535348</v>
       </c>
     </row>
     <row r="1144">
@@ -22603,7 +22603,7 @@
         <v>20</v>
       </c>
       <c r="D1236">
-        <v>0.0009757525491535347</v>
+        <v>0.0009757525491535348</v>
       </c>
     </row>
     <row r="1237">
@@ -22765,7 +22765,7 @@
         <v>20</v>
       </c>
       <c r="D1245">
-        <v>0.0009757525491535347</v>
+        <v>0.0009757525491535348</v>
       </c>
     </row>
     <row r="1246">
@@ -23377,7 +23377,7 @@
         <v>19</v>
       </c>
       <c r="D1279">
-        <v>0.0009269649216958579</v>
+        <v>0.000926964921695858</v>
       </c>
     </row>
     <row r="1280">
@@ -25249,7 +25249,7 @@
         <v>19</v>
       </c>
       <c r="D1383">
-        <v>0.0009269649216958579</v>
+        <v>0.000926964921695858</v>
       </c>
     </row>
     <row r="1384">
@@ -26833,7 +26833,7 @@
         <v>19</v>
       </c>
       <c r="D1471">
-        <v>0.0009269649216958579</v>
+        <v>0.000926964921695858</v>
       </c>
     </row>
     <row r="1472">
@@ -27103,7 +27103,7 @@
         <v>19</v>
       </c>
       <c r="D1486">
-        <v>0.0009269649216958579</v>
+        <v>0.000926964921695858</v>
       </c>
     </row>
     <row r="1487">
@@ -27157,7 +27157,7 @@
         <v>20</v>
       </c>
       <c r="D1489">
-        <v>0.0009757525491535347</v>
+        <v>0.0009757525491535348</v>
       </c>
     </row>
   </sheetData>
